--- a/content-calendar.xlsx
+++ b/content-calendar.xlsx
@@ -1,55 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Content Calendar" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Calendar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="3">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00153F35"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,14 +62,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +222,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +256,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +290,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,112 +425,277 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="55.83203125" customWidth="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Tanggal</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Judul</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Format</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Platform</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="F1" t="str">
-        <v>PIC</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Brief</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tanggal</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Judul</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PIC</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Brief</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>2026-11-20</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Contoh: Profil sekolah</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Reels</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Instagram</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Ide</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Tim Video</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Ganti baris contoh ini dengan rencana konten.</v>
+      <c r="A2" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Foto calon model SPMB</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Terjadwal</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Tim Foto</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Foto siswa dengan baju yayasan untuk kebutuhan promosi SPMB. Pastikan izin dokumentasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Teaser SPMB 2027/2028</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Reels</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Ide</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Tim Video</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Bangun rasa penasaran tentang penerimaan siswa baru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Kenalan dengan SDS IT Madani</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Brief</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Tim Desain</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Kenalkan lingkungan sekolah, program unggulan, dan nilai Islami.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Keseruan belajar di kelas</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Reels</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Produksi</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Tim Video</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Tampilkan aktivitas belajar yang aktif dan menyenangkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Fasilitas sekolah</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Ide</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Tim Desain</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Sorot fasilitas belajar dan lingkungan sekolah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Mengapa memilih SDS IT Madani?</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Reels</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Ide</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Tim Video</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Konten keunggulan sekolah dengan narasi singkat.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/content-calendar.xlsx
+++ b/content-calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yusri\Downloads\files (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B67FB93-B91B-4895-9F03-C6E3FBF78CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70981B7D-0A66-4D52-BD48-540BF017806A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="-120" windowWidth="28320" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
   <si>
     <t>Tanggal</t>
   </si>
@@ -85,34 +85,13 @@
     <t>Bangun rasa penasaran tentang penerimaan siswa baru.</t>
   </si>
   <si>
-    <t>Carousel</t>
-  </si>
-  <si>
-    <t>Tim Desain</t>
-  </si>
-  <si>
     <t>Keseruan belajar di kelas</t>
-  </si>
-  <si>
-    <t>TikTok</t>
   </si>
   <si>
     <t>Produksi</t>
   </si>
   <si>
     <t>Tampilkan aktivitas belajar yang aktif dan menyenangkan.</t>
-  </si>
-  <si>
-    <t>Fasilitas sekolah</t>
-  </si>
-  <si>
-    <t>Sorot fasilitas belajar dan lingkungan sekolah.</t>
-  </si>
-  <si>
-    <t>Mengapa memilih SDS IT Madani?</t>
-  </si>
-  <si>
-    <t>Konten keunggulan sekolah dengan narasi singkat.</t>
   </si>
   <si>
     <t>Petunjuk pengisian (website hanya membaca sheet pertama: Content Calendar)</t>
@@ -155,6 +134,50 @@
   </si>
   <si>
     <t>https://www.instagram.com/reel/DdUJ4mOCXhr/?exln=YTN1bWJuZWc5ZmQ1</t>
+  </si>
+  <si>
+    <t>Promosi SPMB (video AI cara mendaftar di SDS IT Madani Kayuagung)</t>
+  </si>
+  <si>
+    <t>Visual: Anak datang bersama orang tua, memasuki gerbang SDS IT Madani Kayuagung. Ambil gambar dari belakang, lalu lanjutkan dengan shot papan nama sekolah.
+Dialog / VO:
+“Ayah, Bunda, ingin mendaftarkan putra-putri tercinta di SDS IT Madani Kayuagung? Yuk, simak langkah-langkah pendaftarannya!”
+Visual: Anak dan orang tua berjalan menuju stand SPMB. Petugas menyambut dengan ramah.
+Dialog:
+Petugas: “Assalamu’alaikum, Ayah, Bunda. Selamat datang di SDS IT Madani Kayuagung. Ada yang bisa kami bantu?”
+Orang tua: “Wa’alaikumussalam. Kami ingin mendaftarkan anak kami.”
+Petugas: “Baik, Ayah, Bunda. Silakan, kami bantu proses pendaftarannya.”
+Visual: Petugas menyerahkan formulir, orang tua mengisi data calon siswa, lalu petugas memeriksa formulir.
+VO:
+“Langkah pertama, Ayah dan Bunda mengisi formulir pendaftaran dengan lengkap dan benar. Pastikan seluruh data calon peserta didik sudah sesuai.”
+Visual: Orang tua melakukan pembayaran kepada petugas sesuai prosedur sekolah, kemudian menerima bukti pembayaran.
+VO:
+“Selanjutnya, lakukan pembayaran biaya pendaftaran sesuai ketentuan yang berlaku. Jangan lupa menyimpan bukti pembayaran sebagai arsip.”
+Visual: Orang tua menyerahkan berkas persyaratan kepada petugas. Petugas mengecek kelengkapan dokumen.
+VO:
+“Kemudian, serahkan berkas persyaratan yang diminta oleh panitia SPMB. Pastikan semua dokumen sudah lengkap agar proses pendaftaran berjalan lancar.”
+Visual: Petugas memberikan informasi tahap selanjutnya, orang tua menerima konfirmasi, dan anak tersenyum.
+Dialog:
+Petugas: “Alhamdulillah, proses pendaftaran awal sudah selesai. Untuk informasi tahapan berikutnya, Ayah dan Bunda dapat mengikuti arahan dari panitia SPMB.”
+Visual: Anak berjalan memasuki lingkungan sekolah, disambung montage fasilitas, ruang kelas, dan aktivitas siswa.
+VO:
+“Mudah, bukan? Yuk, Ayah dan Bunda, daftarkan putra-putri tercinta di SDS IT Madani Kayuagung. Bersama Madani, tumbuh menjadi generasi Qur’ani, berakhlak mulia, dan berprestasi!”
+Teks layar:
+SPMB SDS IT Madani Kayuagung
+Tahun Ajaran 2027/2028
+Informasi pendaftaran: hubungi panitia SPMB.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>info SPMB</t>
+  </si>
+  <si>
+    <t>ide menyusul</t>
+  </si>
+  <si>
+    <t>menyusul</t>
   </si>
 </sst>
 </file>
@@ -635,7 +658,7 @@
         <v>46327</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>15</v>
@@ -650,10 +673,10 @@
         <v>17</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -661,34 +684,34 @@
         <v>46328</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
@@ -697,19 +720,19 @@
         <v>16</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46332</v>
+        <v>46334</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
@@ -724,28 +747,56 @@
         <v>17</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="A8" s="2">
+        <v>46335</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="A9" s="2">
+        <v>46338</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3688,7 +3739,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3696,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3704,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3712,7 +3763,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3720,15 +3771,15 @@
         <v>7</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/content-calendar.xlsx
+++ b/content-calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yusri\Downloads\files (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70981B7D-0A66-4D52-BD48-540BF017806A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1A1DED-8BF1-4E38-82D1-AE53DCC5F9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="-120" windowWidth="28320" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="38">
   <si>
     <t>Tanggal</t>
   </si>
@@ -800,123 +800,291 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="A10" s="2">
+        <v>46341</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="A11" s="2">
+        <v>46342</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="A12" s="2">
+        <v>46345</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="A13" s="2">
+        <v>46348</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="A14" s="2">
+        <v>46349</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="A15" s="2">
+        <v>46352</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="A16" s="2">
+        <v>46355</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="A17" s="2">
+        <v>46356</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="A18" s="2">
+        <v>46359</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="A19" s="2">
+        <v>46362</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="A20" s="2">
+        <v>46363</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="A21" s="2">
+        <v>46366</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
